--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>2101840</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>26.3600006103516</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>25.9400005340576</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>26.1000003814697</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>25.9400005340576</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>2320993</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>26.1599998474121</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>25.4699993133545</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>25.9400005340576</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1899741</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>26.2299995422363</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>25.9099998474121</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>26.1299991607666</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>26.1800003051758</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>4233364</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>27.1700000762939</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>26.1800003051758</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>26.2199993133545</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>27.0699996948242</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>3664961</v>
+        <v>3920598</v>
       </c>
       <c r="C2715" t="n">
-        <v>26.7299995422363</v>
+        <v>26.9500007629395</v>
       </c>
       <c r="D2715" t="n">
-        <v>26</v>
+        <v>25.5699996948242</v>
       </c>
       <c r="E2715" t="n">
-        <v>26.2999992370605</v>
+        <v>26.8500003814697</v>
       </c>
       <c r="F2715" t="n">
-        <v>26.3899993896484</v>
+        <v>26.25</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>2927395</v>
+        <v>3664961</v>
       </c>
       <c r="C2716" t="n">
-        <v>26.3700008392334</v>
+        <v>26.7299995422363</v>
       </c>
       <c r="D2716" t="n">
-        <v>25.5699996948242</v>
+        <v>26</v>
       </c>
       <c r="E2716" t="n">
-        <v>26.1900005340576</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="F2716" t="n">
-        <v>25.6599998474121</v>
+        <v>26.3899993896484</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>3678801</v>
+        <v>2927395</v>
       </c>
       <c r="C2717" t="n">
-        <v>25.6200008392334</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D2717" t="n">
-        <v>25.2700004577637</v>
+        <v>25.5699996948242</v>
       </c>
       <c r="E2717" t="n">
-        <v>25.5799999237061</v>
+        <v>26.1900005340576</v>
       </c>
       <c r="F2717" t="n">
-        <v>25.5699996948242</v>
+        <v>25.6599998474121</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2899502</v>
+        <v>3678801</v>
       </c>
       <c r="C2718" t="n">
-        <v>26.0599994659424</v>
+        <v>25.6200008392334</v>
       </c>
       <c r="D2718" t="n">
+        <v>25.2700004577637</v>
+      </c>
+      <c r="E2718" t="n">
         <v>25.5799999237061</v>
       </c>
-      <c r="E2718" t="n">
-        <v>25.6000003814697</v>
-      </c>
       <c r="F2718" t="n">
-        <v>26.0599994659424</v>
+        <v>25.5699996948242</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>2101840</v>
+        <v>2899502</v>
       </c>
       <c r="C2719" t="n">
-        <v>26.3600006103516</v>
+        <v>26.0599994659424</v>
       </c>
       <c r="D2719" t="n">
-        <v>25.9400005340576</v>
+        <v>25.5799999237061</v>
       </c>
       <c r="E2719" t="n">
-        <v>26.1000003814697</v>
+        <v>25.6000003814697</v>
       </c>
       <c r="F2719" t="n">
-        <v>25.9400005340576</v>
+        <v>26.0599994659424</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>2320993</v>
+        <v>2101840</v>
       </c>
       <c r="C2720" t="n">
-        <v>26.1599998474121</v>
+        <v>26.3600006103516</v>
       </c>
       <c r="D2720" t="n">
-        <v>25.4699993133545</v>
+        <v>25.9400005340576</v>
       </c>
       <c r="E2720" t="n">
-        <v>25.7999992370605</v>
+        <v>26.1000003814697</v>
       </c>
       <c r="F2720" t="n">
         <v>25.9400005340576</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1899741</v>
+        <v>2320993</v>
       </c>
       <c r="C2721" t="n">
-        <v>26.2299995422363</v>
+        <v>26.1599998474121</v>
       </c>
       <c r="D2721" t="n">
-        <v>25.9099998474121</v>
+        <v>25.4699993133545</v>
       </c>
       <c r="E2721" t="n">
-        <v>26.1299991607666</v>
+        <v>25.7999992370605</v>
       </c>
       <c r="F2721" t="n">
-        <v>26.1800003051758</v>
+        <v>25.9400005340576</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>4233364</v>
+        <v>1899741</v>
       </c>
       <c r="C2722" t="n">
-        <v>27.1700000762939</v>
+        <v>26.2299995422363</v>
       </c>
       <c r="D2722" t="n">
+        <v>25.9099998474121</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>26.1299991607666</v>
+      </c>
+      <c r="F2722" t="n">
         <v>26.1800003051758</v>
       </c>
-      <c r="E2722" t="n">
-        <v>26.2199993133545</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>27.0699996948242</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>19618076</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>27.2000007629395</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>26.6900005340576</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>26.9899997711182</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>26.8899993896484</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>24.5</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>24.6800003051758</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2992275</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>25.0599994659424</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>24.6599998474121</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>24.8299999237061</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>24.8299999237061</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>24.7999992370605</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>6490026</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>24.7700004577637</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>23.9799995422363</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>24.6499996185303</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>24.6499996185303</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>24.0400009155273</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>4126910</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>24.2399997711182</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>23.7399997711182</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>23.8700008392334</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>23.8700008392334</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>23.8799991607666</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>3596472</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>24.1800003051758</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>23.8400001525879</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>24.0400009155273</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2708463</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>24.4500007629395</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>24.3500003814697</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
